--- a/data/performance/daily/signal_list_2026-05-07.xlsx
+++ b/data/performance/daily/signal_list_2026-05-07.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
